--- a/downloads/arbeitsdateien/09_Zoo_2NF_zu_3NF.xlsx
+++ b/downloads/arbeitsdateien/09_Zoo_2NF_zu_3NF.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GEHEGE_TIER" sheetId="1" r:id="Rf1c386b6e56f43ff"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GEHEGE" sheetId="2" r:id="R52e28fd43e5b41b3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GEHEGE_TIER" sheetId="1" r:id="Rd7d36d3402ec4483"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GEHEGE" sheetId="2" r:id="R42b1b968340f498f"/>
   </x:sheets>
 </x:workbook>
 </file>
